--- a/docs/ejemplos-importacion/ejemplo-facturas-emitidas-2026.xlsx
+++ b/docs/ejemplos-importacion/ejemplo-facturas-emitidas-2026.xlsx
@@ -94,10 +94,10 @@
     <t xml:space="preserve">2026-006</t>
   </si>
   <si>
+    <t xml:space="preserve">3T</t>
+  </si>
+  <si>
     <t xml:space="preserve">2026-007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3T</t>
   </si>
   <si>
     <t xml:space="preserve">2026-008</t>
@@ -437,7 +437,7 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s">
         <v>16</v>
@@ -446,7 +446,7 @@
         <v>46213</v>
       </c>
       <c r="E12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F12" t="s">
         <v>18</v>
@@ -475,7 +475,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C13" t="s">
         <v>16</v>
@@ -513,7 +513,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C14" t="s">
         <v>16</v>
